--- a/data/trans_orig/Q5401-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5401-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14741</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20982</t>
+          <t>21465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29982</t>
+          <t>29949</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>21657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42504</t>
+          <t>42601</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36170</t>
+          <t>36027</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>58906</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62705</t>
+          <t>62442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94303</t>
+          <t>94246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>241137</t>
+          <t>242692</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>264305</t>
+          <t>265432</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>268512</t>
+          <t>270554</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>295465</t>
+          <t>296056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>517933</t>
+          <t>519172</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>553784</t>
+          <t>555535</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,41%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30878</t>
+          <t>32207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24791</t>
+          <t>26378</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48729</t>
+          <t>49751</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43744</t>
+          <t>44090</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73939</t>
+          <t>74082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42267</t>
+          <t>41461</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66023</t>
+          <t>66218</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94855</t>
+          <t>94208</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>130756</t>
+          <t>129588</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>141272</t>
+          <t>143258</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>189528</t>
+          <t>184931</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120679</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147477</t>
+          <t>148612</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167596</t>
+          <t>168555</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>206027</t>
+          <t>204423</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296597</t>
+          <t>297465</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>346738</t>
+          <t>345350</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,51%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41790</t>
+          <t>41149</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35704</t>
+          <t>37059</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64637</t>
+          <t>65040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62026</t>
+          <t>62533</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97972</t>
+          <t>96481</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69581</t>
+          <t>69075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101492</t>
+          <t>103252</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136953</t>
+          <t>136621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182362</t>
+          <t>180706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>214501</t>
+          <t>216785</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>269046</t>
+          <t>270684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>369604</t>
+          <t>367864</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>404284</t>
+          <t>405105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>442243</t>
+          <t>444283</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>492768</t>
+          <t>493120</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>826571</t>
+          <t>829621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>889077</t>
+          <t>888570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,35%</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23122</t>
+          <t>24987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23268</t>
+          <t>23672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40897</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>18752</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38370</t>
+          <t>40116</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>35881</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64071</t>
+          <t>61323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60314</t>
+          <t>59466</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93466</t>
+          <t>94816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>254588</t>
+          <t>253725</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>279293</t>
+          <t>279555</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>273989</t>
+          <t>276682</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>303521</t>
+          <t>305293</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>538855</t>
+          <t>536905</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>576027</t>
+          <t>576186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29554</t>
+          <t>29353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55778</t>
+          <t>56436</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66612</t>
+          <t>64538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100354</t>
+          <t>99000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101722</t>
+          <t>103184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141728</t>
+          <t>146102</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43399</t>
+          <t>43703</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72786</t>
+          <t>71838</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>87973</t>
+          <t>87879</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>123669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>138654</t>
+          <t>138787</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>185790</t>
+          <t>186890</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>136558</t>
+          <t>135846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>169653</t>
+          <t>168279</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>182419</t>
+          <t>182087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>224147</t>
+          <t>223107</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>331022</t>
+          <t>326487</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>381255</t>
+          <t>383836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>60,08%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70021</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79103</t>
+          <t>77879</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>116736</t>
+          <t>114552</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>126783</t>
+          <t>128282</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>176251</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66302</t>
+          <t>66315</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102908</t>
+          <t>104273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131518</t>
+          <t>132960</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176386</t>
+          <t>177987</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209938</t>
+          <t>207890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>263875</t>
+          <t>265733</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>398943</t>
+          <t>397822</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>442326</t>
+          <t>443466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>464219</t>
+          <t>467327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>518613</t>
+          <t>518344</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>884710</t>
+          <t>881057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>953322</t>
+          <t>948505</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>20599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9364</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25546</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11857</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>29416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46935</t>
+          <t>46225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77707</t>
+          <t>75025</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62902</t>
+          <t>63345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97065</t>
+          <t>98872</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>290682</t>
+          <t>290217</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>312476</t>
+          <t>312100</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>295312</t>
+          <t>297343</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>326783</t>
+          <t>327901</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>597446</t>
+          <t>596983</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>633473</t>
+          <t>634358</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24314</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45519</t>
+          <t>44895</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32845</t>
+          <t>32460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61007</t>
+          <t>61565</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62005</t>
+          <t>64640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>98066</t>
+          <t>98583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37888</t>
+          <t>36806</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60426</t>
+          <t>60650</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>105072</t>
+          <t>105360</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>145706</t>
+          <t>144444</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>150121</t>
+          <t>149570</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>198165</t>
+          <t>197091</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161598</t>
+          <t>161716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187638</t>
+          <t>189147</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>206073</t>
+          <t>209464</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>251164</t>
+          <t>253454</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>377705</t>
+          <t>380278</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>430760</t>
+          <t>431165</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,61%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34856</t>
+          <t>34604</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59064</t>
+          <t>58111</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>34955</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68298</t>
+          <t>66474</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>78253</t>
+          <t>77294</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>117884</t>
+          <t>115569</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52557</t>
+          <t>54213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81906</t>
+          <t>82250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158314</t>
+          <t>158633</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>211570</t>
+          <t>211814</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223373</t>
+          <t>219475</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282504</t>
+          <t>279484</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>460230</t>
+          <t>460615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>496806</t>
+          <t>496080</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>515861</t>
+          <t>515447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>569273</t>
+          <t>573374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>989697</t>
+          <t>991180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1052949</t>
+          <t>1055888</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>12110</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18646</t>
+          <t>18191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5592,32 +5592,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>24552</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>17097</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33257</t>
+          <t>32498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27762</t>
+          <t>30943</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19722</t>
+          <t>23364</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35473</t>
+          <t>40571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50613</t>
+          <t>55732</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>46755</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80969</t>
+          <t>66794</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>78374</t>
+          <t>86675</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38728</t>
+          <t>73900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104223</t>
+          <t>100565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>327409</t>
+          <t>362884</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>318526</t>
+          <t>352306</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>337183</t>
+          <t>372351</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>546242</t>
+          <t>370324</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>509917</t>
+          <t>359157</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>583335</t>
+          <t>381530</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>873649</t>
+          <t>733208</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>842241</t>
+          <t>716814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>925555</t>
+          <t>747997</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>88,58%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>367450</t>
+          <t>406269</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>367450</t>
+          <t>406269</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>367450</t>
+          <t>406269</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607393</t>
+          <t>438166</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607393</t>
+          <t>438166</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>607393</t>
+          <t>438166</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>974842</t>
+          <t>844435</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>974842</t>
+          <t>844435</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>974842</t>
+          <t>844435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>36567</t>
+          <t>38984</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28131</t>
+          <t>31007</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45440</t>
+          <t>50540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>88487</t>
+          <t>95518</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76354</t>
+          <t>82465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101420</t>
+          <t>108374</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>125054</t>
+          <t>134502</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109751</t>
+          <t>119055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140012</t>
+          <t>151349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57739</t>
+          <t>61890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48217</t>
+          <t>50681</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69612</t>
+          <t>73956</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6126,17 +6126,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>135285</t>
+          <t>147606</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>122159</t>
+          <t>132764</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>150300</t>
+          <t>162642</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>193024</t>
+          <t>209496</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>176653</t>
+          <t>191398</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>210387</t>
+          <t>227772</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>207785</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174078</t>
+          <t>194548</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>198702</t>
+          <t>220801</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>202059</t>
+          <t>221485</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>186478</t>
+          <t>206468</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>217032</t>
+          <t>236757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>389161</t>
+          <t>429270</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>369869</t>
+          <t>407935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>408078</t>
+          <t>449714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,16%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>281408</t>
+          <t>308659</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281408</t>
+          <t>308659</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281408</t>
+          <t>308659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>707239</t>
+          <t>773268</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>707239</t>
+          <t>773268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>707239</t>
+          <t>773268</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48847</t>
+          <t>51426</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39042</t>
+          <t>41678</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60578</t>
+          <t>62648</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>99025</t>
+          <t>107629</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49995</t>
+          <t>93031</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>128406</t>
+          <t>123595</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>147872</t>
+          <t>159054</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96701</t>
+          <t>141948</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>175081</t>
+          <t>178254</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85501</t>
+          <t>92834</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72942</t>
+          <t>78750</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99479</t>
+          <t>107664</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>185898</t>
+          <t>203338</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93536</t>
+          <t>184564</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>238004</t>
+          <t>224710</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>271399</t>
+          <t>296171</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>178193</t>
+          <t>272527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>318079</t>
+          <t>320248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>514510</t>
+          <t>570669</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>497166</t>
+          <t>552732</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>529344</t>
+          <t>587790</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>748301</t>
+          <t>591809</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>671621</t>
+          <t>569667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>885311</t>
+          <t>612395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1262810</t>
+          <t>1162477</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1197340</t>
+          <t>1133967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1409590</t>
+          <t>1190182</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>73,57%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>648858</t>
+          <t>714928</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>648858</t>
+          <t>714928</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>648858</t>
+          <t>714928</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1033224</t>
+          <t>902775</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1033224</t>
+          <t>902775</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1033224</t>
+          <t>902775</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1682081</t>
+          <t>1617703</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1682081</t>
+          <t>1617703</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1682081</t>
+          <t>1617703</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
